--- a/scripts/DoAn4_Bemori/test/cases/test_TK.xlsx
+++ b/scripts/DoAn4_Bemori/test/cases/test_TK.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Đồ án 4\DoAn4\scripts\DoAn4_Bemori\test\cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921605D6-6DB2-4CB7-AA6A-68C05FD727A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48A8D0D-0941-4916-8441-1CFF92EC37B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,9 +78,6 @@
     <t>VERIFY_ELEMENT_PRESENT</t>
   </si>
   <si>
-    <t>txtKoTimThay</t>
-  </si>
-  <si>
     <t>Không có kết quả</t>
   </si>
   <si>
@@ -88,6 +85,9 @@
   </si>
   <si>
     <t>IS_ELEMENT_PRESENT:cboTimThay</t>
+  </si>
+  <si>
+    <t>lblKoTimThay</t>
   </si>
 </sst>
 </file>
@@ -514,7 +514,7 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -539,7 +539,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -547,7 +547,7 @@
         <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D9" s="2"/>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -568,7 +568,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
